--- a/tame_output/ON/bt/strategyON_20231108.xlsx
+++ b/tame_output/ON/bt/strategyON_20231108.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,17 +623,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.3%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.8%</t>
+          <t>102.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.2%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.0%</t>
+          <t>132.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.2%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1774"/>
+  <dimension ref="A1:G1775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.073204449978263</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42328,6 +42328,29 @@
       </c>
       <c r="G1774" t="n">
         <v>4.36402415471628</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="2" t="n">
+        <v>45237</v>
+      </c>
+      <c r="B1775" t="n">
+        <v>3.085454620141824</v>
+      </c>
+      <c r="C1775" t="n">
+        <v>3.05676708948516</v>
+      </c>
+      <c r="D1775" t="n">
+        <v>1.550043055721617</v>
+      </c>
+      <c r="E1775" t="n">
+        <v>3.67642788746006</v>
+      </c>
+      <c r="F1775" t="n">
+        <v>2.175821104491166</v>
+      </c>
+      <c r="G1775" t="n">
+        <v>4.362259752179861</v>
       </c>
     </row>
   </sheetData>
